--- a/yellow-server/data/results/外卖收货地址高风险统计.xlsx
+++ b/yellow-server/data/results/外卖收货地址高风险统计.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:I3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -408,6 +408,24 @@
       </c>
       <c r="C1" t="str">
         <v>姓名证件列表</v>
+      </c>
+      <c r="D1" t="str">
+        <v>异常资金</v>
+      </c>
+      <c r="E1" t="str">
+        <v>入住次数</v>
+      </c>
+      <c r="F1" t="str">
+        <v>同住男人数</v>
+      </c>
+      <c r="G1" t="str">
+        <v>前科次数</v>
+      </c>
+      <c r="H1" t="str">
+        <v>前科人员</v>
+      </c>
+      <c r="I1" t="str">
+        <v>前科情况</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
@@ -427,6 +445,24 @@
 姓名：小刚——证件号码：310227199002301008——原始地址：松江公寓 (129)
 姓名：小金——证件号码：310227199002301009——原始地址：松江公寓 (130)</v>
       </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
@@ -439,10 +475,28 @@
         <v xml:space="preserve">姓名：老王——证件号码：310227199002301002——原始地址：养生SPA (养生spa)
 姓名：小钱——证件号码：310227199002301010——原始地址：养生SPA (养生spa)</v>
       </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/yellow-server/data/results/外卖收货地址高风险统计.xlsx
+++ b/yellow-server/data/results/外卖收货地址高风险统计.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:C3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -408,24 +408,6 @@
       </c>
       <c r="C1" t="str">
         <v>姓名证件列表</v>
-      </c>
-      <c r="D1" t="str">
-        <v>异常资金</v>
-      </c>
-      <c r="E1" t="str">
-        <v>入住次数</v>
-      </c>
-      <c r="F1" t="str">
-        <v>同住男人数</v>
-      </c>
-      <c r="G1" t="str">
-        <v>前科次数</v>
-      </c>
-      <c r="H1" t="str">
-        <v>前科人员</v>
-      </c>
-      <c r="I1" t="str">
-        <v>前科情况</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
@@ -445,24 +427,6 @@
 姓名：小刚——证件号码：310227199002301008——原始地址：松江公寓 (129)
 姓名：小金——证件号码：310227199002301009——原始地址：松江公寓 (130)</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
@@ -475,28 +439,10 @@
         <v xml:space="preserve">姓名：老王——证件号码：310227199002301002——原始地址：养生SPA (养生spa)
 姓名：小钱——证件号码：310227199002301010——原始地址：养生SPA (养生spa)</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>